--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +530,949 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>FECHA_DETECCION</t>
+          <t>PROGINSTI</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>FECHA_OBTENCION</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>DIVISIÓN UNINORTE</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>DIVISIÓN UNINORTE</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>117953</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Doctorado en Antropología</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>104</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Antropología y  artes liberales</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>117953-104</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1711</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>117949</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FISIOTERAPIA EN CUIDADO CRÍTICO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>117949-30</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1729</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>117948</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Especialización en Gastroenterología Pediátrica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>136</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>117948-136</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2829</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>117956</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Maestría en Educación STEM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>36</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>117956-36</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2829</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>117957</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Maestría en Educación STEM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>117957-36</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2830</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA IBEROAMERICANA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>117947</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE LA SALUD PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>28</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>45763</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>117947-28</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9913</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>117950</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Especialización en Derecho Comercial</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>117950-24</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9913</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>117951</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CADENA DE SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>117951-24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9926</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>117952</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Especialización en Dirección Comercial y Ventas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>117952-24</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Activo</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,117 +421,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NIVEL_DE_FORMACIÓN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -603,7 +591,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -706,7 +694,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -809,7 +797,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -912,7 +900,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -1015,7 +1003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1118,7 +1106,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>45763</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1221,7 +1209,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1324,7 +1312,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1427,7 +1415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O10" t="inlineStr">

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,6 +1462,952 @@
         </is>
       </c>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>118534</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Especialización en Contabilidad Internacional</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>118533</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Especialización en Contratación Estatal</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>118532</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Maestría en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>118535</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Maestría en Gerencia de Proyectos</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>42</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>118529</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN EDUCACIÓN DIGITAL Y DISEÑO DE APRENDIZAJES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>86</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>118527</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DEL BIENESTAR PSICOSOCIAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>28</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>118528</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ATENCIÓN DEL BIENESTAR PSICOSOCIAL COMUNITARIO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>118522</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIENCIA DE DATOS Y APLICACIONES MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>118525</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Maestría en Derechos Humanos y Protección a Victimas</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>40</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CESMAG - UNICESMAG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>118526</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Especialización en Marketing Digital</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1468,10 +1465,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1709</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1515,7 +1510,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1561,10 +1556,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1709</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1608,7 +1601,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1654,10 +1647,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1709</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1701,7 +1692,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1747,10 +1738,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1709</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1794,7 +1783,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1840,10 +1829,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1728</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1887,7 +1874,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1933,10 +1920,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1728</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1980,7 +1965,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2026,10 +2011,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1728</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2081,7 +2064,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -2127,10 +2110,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1728</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2182,7 +2163,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -2228,10 +2209,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1728</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2275,7 +2254,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -2321,10 +2300,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2744</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2368,7 +2345,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="O20" t="inlineStr">

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2388,107 @@
         </is>
       </c>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>118538</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Especialización en Derecho del Trabajo y de la Seguridad Social</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
